--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121159461</v>
+        <v>121160047</v>
       </c>
       <c r="B6" t="n">
-        <v>90973</v>
+        <v>78598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578417</v>
+        <v>578444</v>
       </c>
       <c r="R6" t="n">
-        <v>7079075</v>
+        <v>7079067</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121160047</v>
+        <v>121159461</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>90973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578444</v>
+        <v>578417</v>
       </c>
       <c r="R7" t="n">
-        <v>7079067</v>
+        <v>7079075</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121160235</v>
+        <v>121163009</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578455</v>
+        <v>578398</v>
       </c>
       <c r="R2" t="n">
-        <v>7079102</v>
+        <v>7079154</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121160001</v>
+        <v>121162474</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578458</v>
+        <v>578361</v>
       </c>
       <c r="R3" t="n">
-        <v>7079073</v>
+        <v>7079111</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159422</v>
+        <v>121160001</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578397</v>
+        <v>578458</v>
       </c>
       <c r="R4" t="n">
-        <v>7079082</v>
+        <v>7079073</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121162913</v>
+        <v>121159461</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578341</v>
+        <v>578417</v>
       </c>
       <c r="R5" t="n">
-        <v>7079124</v>
+        <v>7079075</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1086,7 @@
         <v>121160047</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159461</v>
+        <v>121162913</v>
       </c>
       <c r="B7" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578417</v>
+        <v>578341</v>
       </c>
       <c r="R7" t="n">
-        <v>7079075</v>
+        <v>7079124</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121162955</v>
+        <v>121160235</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578383</v>
+        <v>578455</v>
       </c>
       <c r="R8" t="n">
-        <v>7079145</v>
+        <v>7079102</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121162474</v>
+        <v>121162962</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578361</v>
+        <v>578383</v>
       </c>
       <c r="R9" t="n">
-        <v>7079111</v>
+        <v>7079145</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121162962</v>
+        <v>121159422</v>
       </c>
       <c r="B10" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578383</v>
+        <v>578397</v>
       </c>
       <c r="R10" t="n">
-        <v>7079145</v>
+        <v>7079082</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121163009</v>
+        <v>121162955</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578398</v>
+        <v>578383</v>
       </c>
       <c r="R11" t="n">
-        <v>7079154</v>
+        <v>7079145</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121159461</v>
+        <v>121160047</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578417</v>
+        <v>578444</v>
       </c>
       <c r="R5" t="n">
-        <v>7079075</v>
+        <v>7079067</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121160047</v>
+        <v>121159461</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578444</v>
+        <v>578417</v>
       </c>
       <c r="R6" t="n">
-        <v>7079067</v>
+        <v>7079075</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121160047</v>
+        <v>121159461</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578444</v>
+        <v>578417</v>
       </c>
       <c r="R5" t="n">
-        <v>7079067</v>
+        <v>7079075</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121159461</v>
+        <v>121160047</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578417</v>
+        <v>578444</v>
       </c>
       <c r="R6" t="n">
-        <v>7079075</v>
+        <v>7079067</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121162962</v>
+        <v>121159422</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578383</v>
+        <v>578397</v>
       </c>
       <c r="R9" t="n">
-        <v>7079145</v>
+        <v>7079082</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121159422</v>
+        <v>121162962</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R10" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121163009</v>
+        <v>121160047</v>
       </c>
       <c r="B2" t="n">
         <v>78601</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578398</v>
+        <v>578444</v>
       </c>
       <c r="R2" t="n">
-        <v>7079154</v>
+        <v>7079067</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121162474</v>
+        <v>121163009</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578361</v>
+        <v>578398</v>
       </c>
       <c r="R3" t="n">
-        <v>7079111</v>
+        <v>7079154</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121160001</v>
+        <v>121162913</v>
       </c>
       <c r="B4" t="n">
         <v>79682</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578458</v>
+        <v>578341</v>
       </c>
       <c r="R4" t="n">
-        <v>7079073</v>
+        <v>7079124</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121159461</v>
+        <v>121160235</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578417</v>
+        <v>578455</v>
       </c>
       <c r="R5" t="n">
-        <v>7079075</v>
+        <v>7079102</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121160047</v>
+        <v>121159422</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578444</v>
+        <v>578397</v>
       </c>
       <c r="R6" t="n">
-        <v>7079067</v>
+        <v>7079082</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121162913</v>
+        <v>121162955</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578341</v>
+        <v>578383</v>
       </c>
       <c r="R7" t="n">
-        <v>7079124</v>
+        <v>7079145</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121160235</v>
+        <v>121162474</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578455</v>
+        <v>578361</v>
       </c>
       <c r="R8" t="n">
-        <v>7079102</v>
+        <v>7079111</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121159422</v>
+        <v>121162962</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R9" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121162962</v>
+        <v>121159461</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578383</v>
+        <v>578417</v>
       </c>
       <c r="R10" t="n">
-        <v>7079145</v>
+        <v>7079075</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121162955</v>
+        <v>121160001</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578383</v>
+        <v>578458</v>
       </c>
       <c r="R11" t="n">
-        <v>7079145</v>
+        <v>7079073</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121160235</v>
+        <v>121159422</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578455</v>
+        <v>578397</v>
       </c>
       <c r="R5" t="n">
-        <v>7079102</v>
+        <v>7079082</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121159422</v>
+        <v>121162955</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R6" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121162955</v>
+        <v>121160235</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578383</v>
+        <v>578455</v>
       </c>
       <c r="R7" t="n">
-        <v>7079145</v>
+        <v>7079102</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121160047</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121163009</v>
+        <v>121160001</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578398</v>
+        <v>578458</v>
       </c>
       <c r="R3" t="n">
-        <v>7079154</v>
+        <v>7079073</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121162913</v>
+        <v>121159422</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578341</v>
+        <v>578397</v>
       </c>
       <c r="R4" t="n">
-        <v>7079124</v>
+        <v>7079082</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121159422</v>
+        <v>121162962</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R5" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121162955</v>
+        <v>121162474</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578383</v>
+        <v>578361</v>
       </c>
       <c r="R6" t="n">
-        <v>7079145</v>
+        <v>7079111</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,7 +1188,7 @@
         <v>121160235</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121162474</v>
+        <v>121159461</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>90995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578361</v>
+        <v>578417</v>
       </c>
       <c r="R8" t="n">
-        <v>7079111</v>
+        <v>7079075</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121162962</v>
+        <v>121162913</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578383</v>
+        <v>578341</v>
       </c>
       <c r="R9" t="n">
-        <v>7079145</v>
+        <v>7079124</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121159461</v>
+        <v>121162955</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578417</v>
+        <v>578383</v>
       </c>
       <c r="R10" t="n">
-        <v>7079075</v>
+        <v>7079145</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121160001</v>
+        <v>121163009</v>
       </c>
       <c r="B11" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578458</v>
+        <v>578398</v>
       </c>
       <c r="R11" t="n">
-        <v>7079073</v>
+        <v>7079154</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121160047</v>
+        <v>121162913</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578444</v>
+        <v>578341</v>
       </c>
       <c r="R2" t="n">
-        <v>7079067</v>
+        <v>7079124</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121160001</v>
+        <v>121160047</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578458</v>
+        <v>578444</v>
       </c>
       <c r="R3" t="n">
-        <v>7079073</v>
+        <v>7079067</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159422</v>
+        <v>121162955</v>
       </c>
       <c r="B4" t="n">
         <v>78604</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R4" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121162962</v>
+        <v>121162474</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578383</v>
+        <v>578361</v>
       </c>
       <c r="R5" t="n">
-        <v>7079145</v>
+        <v>7079111</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121162474</v>
+        <v>121160001</v>
       </c>
       <c r="B6" t="n">
         <v>79685</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578361</v>
+        <v>578458</v>
       </c>
       <c r="R6" t="n">
-        <v>7079111</v>
+        <v>7079073</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121160235</v>
+        <v>121159461</v>
       </c>
       <c r="B7" t="n">
-        <v>90709</v>
+        <v>90996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578455</v>
+        <v>578417</v>
       </c>
       <c r="R7" t="n">
-        <v>7079102</v>
+        <v>7079075</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159461</v>
+        <v>121159422</v>
       </c>
       <c r="B8" t="n">
-        <v>90995</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578417</v>
+        <v>578397</v>
       </c>
       <c r="R8" t="n">
-        <v>7079075</v>
+        <v>7079082</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121162913</v>
+        <v>121163009</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578341</v>
+        <v>578398</v>
       </c>
       <c r="R9" t="n">
-        <v>7079124</v>
+        <v>7079154</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121162955</v>
+        <v>121162962</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121163009</v>
+        <v>121160235</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578398</v>
+        <v>578455</v>
       </c>
       <c r="R11" t="n">
-        <v>7079154</v>
+        <v>7079102</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121162913</v>
+        <v>121162962</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578341</v>
+        <v>578383</v>
       </c>
       <c r="R2" t="n">
-        <v>7079124</v>
+        <v>7079145</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121160047</v>
+        <v>121162474</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578444</v>
+        <v>578361</v>
       </c>
       <c r="R3" t="n">
-        <v>7079067</v>
+        <v>7079111</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121162955</v>
+        <v>121160235</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578383</v>
+        <v>578455</v>
       </c>
       <c r="R4" t="n">
-        <v>7079145</v>
+        <v>7079102</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121162474</v>
+        <v>121163009</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578361</v>
+        <v>578398</v>
       </c>
       <c r="R5" t="n">
-        <v>7079111</v>
+        <v>7079154</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121160001</v>
+        <v>121162955</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578458</v>
+        <v>578383</v>
       </c>
       <c r="R6" t="n">
-        <v>7079073</v>
+        <v>7079145</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121159461</v>
+        <v>121160047</v>
       </c>
       <c r="B7" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578417</v>
+        <v>578444</v>
       </c>
       <c r="R7" t="n">
-        <v>7079075</v>
+        <v>7079067</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
         <v>121159422</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121163009</v>
+        <v>121159461</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>90999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578398</v>
+        <v>578417</v>
       </c>
       <c r="R9" t="n">
-        <v>7079154</v>
+        <v>7079075</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121162962</v>
+        <v>121162913</v>
       </c>
       <c r="B10" t="n">
-        <v>57504</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578383</v>
+        <v>578341</v>
       </c>
       <c r="R10" t="n">
-        <v>7079145</v>
+        <v>7079124</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121160235</v>
+        <v>121160001</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578455</v>
+        <v>578458</v>
       </c>
       <c r="R11" t="n">
-        <v>7079102</v>
+        <v>7079073</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121162962</v>
+        <v>121163009</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578383</v>
+        <v>578398</v>
       </c>
       <c r="R2" t="n">
-        <v>7079145</v>
+        <v>7079154</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121162474</v>
+        <v>121162962</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578361</v>
+        <v>578383</v>
       </c>
       <c r="R3" t="n">
-        <v>7079111</v>
+        <v>7079145</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121160235</v>
+        <v>121159422</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578455</v>
+        <v>578397</v>
       </c>
       <c r="R4" t="n">
-        <v>7079102</v>
+        <v>7079082</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121163009</v>
+        <v>121160235</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578398</v>
+        <v>578455</v>
       </c>
       <c r="R5" t="n">
-        <v>7079154</v>
+        <v>7079102</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121162955</v>
+        <v>121160001</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578383</v>
+        <v>578458</v>
       </c>
       <c r="R6" t="n">
-        <v>7079145</v>
+        <v>7079073</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121160047</v>
+        <v>121162913</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578444</v>
+        <v>578341</v>
       </c>
       <c r="R7" t="n">
-        <v>7079067</v>
+        <v>7079124</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121159422</v>
+        <v>121160047</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578397</v>
+        <v>578444</v>
       </c>
       <c r="R8" t="n">
-        <v>7079082</v>
+        <v>7079067</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121159461</v>
+        <v>121162474</v>
       </c>
       <c r="B9" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578417</v>
+        <v>578361</v>
       </c>
       <c r="R9" t="n">
-        <v>7079075</v>
+        <v>7079111</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121162913</v>
+        <v>121159461</v>
       </c>
       <c r="B10" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578341</v>
+        <v>578417</v>
       </c>
       <c r="R10" t="n">
-        <v>7079124</v>
+        <v>7079075</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121160001</v>
+        <v>121162955</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578458</v>
+        <v>578383</v>
       </c>
       <c r="R11" t="n">
-        <v>7079073</v>
+        <v>7079145</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 26468-2024 artfynd.xlsx
+++ b/artfynd/A 26468-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121163009</v>
+        <v>121162913</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578398</v>
+        <v>578341</v>
       </c>
       <c r="R2" t="n">
-        <v>7079154</v>
+        <v>7079124</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121162962</v>
+        <v>121163009</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578383</v>
+        <v>578398</v>
       </c>
       <c r="R3" t="n">
-        <v>7079145</v>
+        <v>7079154</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159422</v>
+        <v>121162955</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578397</v>
+        <v>578383</v>
       </c>
       <c r="R4" t="n">
-        <v>7079082</v>
+        <v>7079145</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121160235</v>
+        <v>121160047</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578455</v>
+        <v>578444</v>
       </c>
       <c r="R5" t="n">
-        <v>7079102</v>
+        <v>7079067</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121160001</v>
+        <v>121159422</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578458</v>
+        <v>578397</v>
       </c>
       <c r="R6" t="n">
-        <v>7079073</v>
+        <v>7079082</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121162913</v>
+        <v>121160001</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578341</v>
+        <v>578458</v>
       </c>
       <c r="R7" t="n">
-        <v>7079124</v>
+        <v>7079073</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121160047</v>
+        <v>121160235</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578444</v>
+        <v>578455</v>
       </c>
       <c r="R8" t="n">
-        <v>7079067</v>
+        <v>7079102</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121162474</v>
+        <v>121162962</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>57508</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578361</v>
+        <v>578383</v>
       </c>
       <c r="R9" t="n">
-        <v>7079111</v>
+        <v>7079145</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121159461</v>
+        <v>121162474</v>
       </c>
       <c r="B10" t="n">
-        <v>90999</v>
+        <v>79689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578417</v>
+        <v>578361</v>
       </c>
       <c r="R10" t="n">
-        <v>7079075</v>
+        <v>7079111</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121162955</v>
+        <v>121159461</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>91005</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Höktjärnen, Ång</t>
+          <t>Lill-Höktjärnen, Lill-Höktjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578383</v>
+        <v>578417</v>
       </c>
       <c r="R11" t="n">
-        <v>7079145</v>
+        <v>7079075</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
